--- a/processed_ruby_restored_xlsx/sc219_ノノＢ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc219_ノノＢ：ＥＮＤ.ss.xlsx
@@ -703,7 +703,8 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Well, she's the teacher, so it's not unnatural, but...</t>
+          <t>Well, she's the teacher, so it's not unnatural,
+but...</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -733,8 +734,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>「Okay, okay, heeeey！ Everyone, please take your seats！
-We're going to start the closing meeting~！」</t>
+          <t>「Okay, okay, heeeey！ Everyone, please take your
+seats！ We're going to start the closing meeting~！」</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1179,8 +1180,8 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>I was a good person, the kids were good too, there was
-nothing to dislike.</t>
+          <t>I was a good person, the kids were good too, there
+was nothing to dislike.</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2575,8 +2576,8 @@
       <c r="B138" s="1" t="inlineStr">
         <is>
           <t>「I became the teacher I dreamed of, met all of you,
-taught classes... it was hard in many ways, but it was
-fun.」</t>
+taught classes... it was hard in many ways, but it
+was fun.」</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2623,8 +2624,8 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan hesitated over her words, but she spoke each
-one as if savoring it.</t>
+          <t>Nono-chan hesitated over her words, but she spoke
+each one as if savoring it.</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -3455,8 +3456,8 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>I'd already said what I needed to say… so all that was
-left was to convey warmth.</t>
+          <t>I'd already said what I needed to say… so all that
+was left was to convey warmth.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -4413,8 +4414,8 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>I told Kikuchiyo-baa-chan that maybe we should've left
-Nono-chan behind.</t>
+          <t>I told Kikuchiyo-baa-chan that maybe we should've
+left Nono-chan behind.</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4696,8 +4697,8 @@
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Thinking that, believing that... I drive the bus today
-as well.</t>
+          <t>Thinking that, believing that... I drive the bus
+today as well.</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4788,8 +4789,8 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>My workload has increased overwhelmingly and I'm dizzy
-every day.</t>
+          <t>My workload has increased overwhelmingly and I'm
+dizzy every day.</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -5743,8 +5744,8 @@
       </c>
       <c r="B346" s="1" t="inlineStr">
         <is>
-          <t>Startled, I ended up calling out to someone who wasn’t
-even there.</t>
+          <t>Startled, I ended up calling out to someone who
+wasn’t even there.</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5985,8 +5986,8 @@
       </c>
       <c r="B362" s="1" t="inlineStr">
         <is>
-          <t>It seemed Kikuchiyo-baa-chan was about to butt in, but
-the broadcast cut off at that moment.</t>
+          <t>It seemed Kikuchiyo-baa-chan was about to butt in,
+but the broadcast cut off at that moment.</t>
         </is>
       </c>
       <c r="C362" t="n">

--- a/processed_ruby_restored_xlsx/sc219_ノノＢ：ＥＮＤ.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc219_ノノＢ：ＥＮＤ.ss.xlsx
@@ -734,8 +734,8 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>「Okay, okay, heeeey！ Everyone, please take your
-seats！ We're going to start the closing meeting~！」</t>
+          <t>Okay, okay, heeeey！ Everyone, please take your seats！
+We're going to start the closing meeting~！</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>I was a good person, the kids were good too, there
+          <t>He was a good person, the kids were good too, there
 was nothing to dislike.</t>
         </is>
       </c>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ Janitor-sensei, what is it？」</t>
+          <t>Yes！ Janitor-sensei, what is it？</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>「Yes... sensei has finished my work here and will be
+          <t>「Yes... sensei has finished his work here and will be
 going home.」</t>
         </is>
       </c>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei... is that okay？」</t>
+          <t>Janitor-sensei... is that okay？</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>「J-Janitor-sensei...？」</t>
+          <t>J-Janitor-sensei...？</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>「...Janitor-sensei！」</t>
+          <t>...Janitor-sensei！</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Nono</t>
+          <t>Nono-chan</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2482,8 +2482,8 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>「Please don't worry. Janitor-sensei, your feelings
-alone are more than enough.」</t>
+          <t>Please don't worry. Janitor-sensei, your feelings
+alone are more than enough.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>What am I doing getting weak now of all times...！</t>
+          <t>What am I doing getting weak now of all times...！"</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>「Alright, alright, everyone, the bell just rang~！」</t>
+          <t>Alright, alright, everyone, the bell just rang~！</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>「Yesss！ Onii-chan teacher~！」</t>
+          <t>Yesss！ Onii-chan teacher~！</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>「Ahh, it's the principal's announcement！」</t>
+          <t>Ahh, it's the principal's announcement！</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>「Oh...？」</t>
+          <t>Oh...？</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>「Huh？ I wonder what it is...？」</t>
+          <t>Huh？ I wonder what it is...？</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>「Yes！ I've gloriously returned！」</t>
+          <t>Yes！ I've gloriously returned！</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -6033,8 +6033,8 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>「Well... that's how it is, so everyone, please keep
-being friendly with each other！」</t>
+          <t>Well... that's how it is, so everyone, please keep
+being friendly with each other！</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="B367" s="1" t="inlineStr">
         <is>
-          <t>「Ah... Nono-chan！」</t>
+          <t>Ah... Nono-chan！</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan...！」</t>
+          <t>Nono-chan...！</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="B371" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan...！」</t>
+          <t>Nono-chan...！</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>「........！」</t>
+          <t>........！</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「Nng... everyone...!!, ~~~!」</t>
+          <t>Nng... everyone...!!, ~~~!</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>「Nono-chan... welcome home.」</t>
+          <t>Nono-chan... welcome home.</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="B385" s="1" t="inlineStr">
         <is>
-          <t>「H-Hajime-san...」</t>
+          <t>H-Hajime-san...</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>「I missed you！ I really missed youuuuuu！」</t>
+          <t>I missed you！ I really missed youuuuuu！</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>「Yeah...！」</t>
+          <t>Yeah...！</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei... I loooove you！！！」</t>
+          <t>Janitor-sensei... I loooove you！！！</t>
         </is>
       </c>
       <c r="C393" t="n">
